--- a/data/Rickenbach (LU)/investment_decision/Rickenbach LU_SFH_until_2004_investment_decision.xlsx
+++ b/data/Rickenbach (LU)/investment_decision/Rickenbach LU_SFH_until_2004_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -471,31 +470,31 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_all_invested_available_unit</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_all_candidate_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>237.4580633003135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -509,30 +508,30 @@
         <v>308275.6996421451</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>239.0667100204335</v>
       </c>
       <c r="G2" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>167.2828321654253</v>
       </c>
       <c r="I2" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>165.6358899432769</v>
       </c>
       <c r="K2" t="n">
         <v>308275.6996421451</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
-        <v>1346.890712566202</v>
+        <v>580.8127791840483</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -546,30 +545,30 @@
         <v>308275.6996421451</v>
       </c>
       <c r="F3" t="n">
-        <v>1381.703563121144</v>
+        <v>677.8404386383608</v>
       </c>
       <c r="G3" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="H3" t="n">
-        <v>1209.53317684394</v>
+        <v>634.9274264350267</v>
       </c>
       <c r="I3" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="J3" t="n">
-        <v>1242.338478351048</v>
+        <v>647.6493509387188</v>
       </c>
       <c r="K3" t="n">
         <v>308275.6996421451</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
-        <v>2021.882150928369</v>
+        <v>1170.346374603491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -583,30 +582,30 @@
         <v>308275.6996421451</v>
       </c>
       <c r="F4" t="n">
-        <v>2176.10980709971</v>
+        <v>1192.06625864851</v>
       </c>
       <c r="G4" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="H4" t="n">
-        <v>1544.039081963746</v>
+        <v>1161.860086871076</v>
       </c>
       <c r="I4" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="J4" t="n">
-        <v>1499.1117168003</v>
+        <v>1150.60521029337</v>
       </c>
       <c r="K4" t="n">
         <v>308275.6996421451</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
-        <v>2440.41737904638</v>
+        <v>1229.760697378278</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -620,30 +619,30 @@
         <v>308275.6996421451</v>
       </c>
       <c r="F5" t="n">
-        <v>2440.41737904638</v>
+        <v>1229.760697378277</v>
       </c>
       <c r="G5" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="H5" t="n">
-        <v>1800.858209977476</v>
+        <v>1229.760697378277</v>
       </c>
       <c r="I5" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="J5" t="n">
-        <v>1808.982674348756</v>
+        <v>1229.760697378274</v>
       </c>
       <c r="K5" t="n">
         <v>308275.6996421451</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
-        <v>2440.41737904638</v>
+        <v>1229.760697378278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -657,26 +656,26 @@
         <v>308275.6996421451</v>
       </c>
       <c r="F6" t="n">
-        <v>2440.41737904638</v>
+        <v>1229.760697378277</v>
       </c>
       <c r="G6" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="H6" t="n">
-        <v>1800.858209977476</v>
+        <v>1229.760697378277</v>
       </c>
       <c r="I6" t="n">
         <v>308275.6996421451</v>
       </c>
       <c r="J6" t="n">
-        <v>1808.982674348756</v>
+        <v>1229.760697378274</v>
       </c>
       <c r="K6" t="n">
         <v>308275.6996421451</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
@@ -684,36 +683,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Rickenbach LU_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Rickenbach LU_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E7" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>297.9274289279234</v>
+        <v>244.4204343742149</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>297.9274289279234</v>
+        <v>244.4204343742149</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
@@ -721,36 +720,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Rickenbach LU_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Rickenbach LU_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E8" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>370.2337669797691</v>
+        <v>303.7407413974283</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>370.2337669797691</v>
+        <v>303.7407413974283</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
@@ -758,36 +757,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Rickenbach LU_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Rickenbach LU_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E9" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>399.3878804797738</v>
+        <v>327.65885162685</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>399.3878804797738</v>
+        <v>327.65885162685</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
@@ -795,36 +794,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Rickenbach LU_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Rickenbach LU_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E10" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>414.3447430215282</v>
+        <v>339.9295003968747</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>414.3447430215282</v>
+        <v>339.9295003968747</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
@@ -832,40 +831,40 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BLVL_VanadiumRedox_s_2 MWh_d_Rickenbach LU_b_SFH_until_2004</t>
+          <t>BLVL_Li-ion_s_12.5 kWh_d_Rickenbach LU_b_SFH_until_2004</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>0.0125</v>
       </c>
       <c r="E11" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>462.4135494632176</v>
+        <v>379.3652737078651</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>423.2091467950974</v>
+        <v>347.2018802129956</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>423.2091467950974</v>
+        <v>347.2018802129956</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0587314826682353</v>
+        <v>0.05032036982041368</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -879,30 +878,30 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0587314826682353</v>
+        <v>0.04975851166511955</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0587314826682353</v>
+        <v>0.05362439721882353</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0587314826682353</v>
+        <v>0.05362439721882353</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0587314826682353</v>
+        <v>0.05362439721882353</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -916,30 +915,30 @@
         <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06128502539294119</v>
+        <v>0.05362439721882353</v>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.06128502539294119</v>
+        <v>0.05617793994352941</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.06128502539294119</v>
+        <v>0.05617793994352941</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
-        <v>0.06128502539294119</v>
+        <v>0.05617793994352941</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -953,30 +952,30 @@
         <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06141624180235293</v>
+        <v>0.05617793994352941</v>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.06141624180235293</v>
+        <v>0.05617793994352941</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06141624180235293</v>
+        <v>0.05617793994352941</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
-        <v>0.06894565356705881</v>
+        <v>0.05873148266823532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -990,30 +989,30 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06894565356705881</v>
+        <v>0.0587314826682353</v>
       </c>
       <c r="G15" t="n">
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06894565356705881</v>
+        <v>0.05907579360278337</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.06894565356705881</v>
+        <v>0.05907579360278332</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
-        <v>0.06894565356705881</v>
+        <v>0.05873148266823532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1027,26 +1026,26 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0.06894565356705881</v>
+        <v>0.0587314826682353</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.06894565356705881</v>
+        <v>0.05907579360278337</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.06894565356705881</v>
+        <v>0.05907579360278333</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B17" t="n">
@@ -1083,7 +1082,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B18" t="n">
@@ -1120,11 +1119,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1.76363589717973</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1138,30 +1137,30 @@
         <v>45.58073763600002</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1.342290021390029</v>
       </c>
       <c r="G19" t="n">
         <v>45.58073763600002</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1.560583462724064</v>
       </c>
       <c r="I19" t="n">
         <v>45.58073763600002</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1.736387063870363</v>
       </c>
       <c r="K19" t="n">
         <v>45.58073763600002</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>5.426278289999977</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1175,30 +1174,30 @@
         <v>45.58073763600002</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>5.426278289999996</v>
       </c>
       <c r="G20" t="n">
         <v>45.58073763600002</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5.243363106021333</v>
       </c>
       <c r="I20" t="n">
         <v>45.58073763600002</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>5.243363106021358</v>
       </c>
       <c r="K20" t="n">
         <v>45.58073763600002</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>5.426278289999977</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1212,26 +1211,26 @@
         <v>45.58073763600002</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>5.426278289999996</v>
       </c>
       <c r="G21" t="n">
         <v>45.58073763600002</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>5.243363106021333</v>
       </c>
       <c r="I21" t="n">
         <v>45.58073763600002</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.243363106021352</v>
       </c>
       <c r="K21" t="n">
         <v>45.58073763600002</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B22" t="n">
@@ -1268,7 +1267,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B23" t="n">
@@ -1305,7 +1304,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B24" t="n">
@@ -1342,7 +1341,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B25" t="n">
@@ -1379,7 +1378,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B26" t="n">
@@ -1416,7 +1415,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B27" t="n">
@@ -1453,7 +1452,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B28" t="n">
@@ -1490,7 +1489,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B29" t="n">
@@ -1527,7 +1526,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B30" t="n">
@@ -1564,7 +1563,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B31" t="n">
@@ -1601,7 +1600,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B32" t="n">
@@ -1638,7 +1637,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B33" t="n">
@@ -1675,7 +1674,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B34" t="n">
@@ -1712,7 +1711,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B35" t="n">
@@ -1749,7 +1748,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B36" t="n">
@@ -1786,7 +1785,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B37" t="n">
@@ -1823,7 +1822,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B38" t="n">
@@ -1860,7 +1859,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B39" t="n">
@@ -1897,7 +1896,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B40" t="n">
@@ -1934,7 +1933,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B41" t="n">
@@ -1971,7 +1970,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B42" t="n">
@@ -2008,7 +2007,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B43" t="n">
@@ -2045,7 +2044,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B44" t="n">
@@ -2082,7 +2081,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B45" t="n">
@@ -2119,7 +2118,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B46" t="n">
@@ -2156,7 +2155,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B47" t="n">
@@ -2193,7 +2192,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B48" t="n">
@@ -2230,7 +2229,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B49" t="n">
@@ -2267,7 +2266,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B50" t="n">
@@ -2304,7 +2303,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B51" t="n">
@@ -2341,11 +2340,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>9.609792842790371</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2359,30 +2358,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F52" t="n">
-        <v>24.74133124293699</v>
+        <v>34.48251564526846</v>
       </c>
       <c r="G52" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H52" t="n">
-        <v>6.456121562560099</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
         <v>99.00182237673239</v>
       </c>
       <c r="J52" t="n">
-        <v>7.732892924913038</v>
+        <v>8.977855918526817</v>
       </c>
       <c r="K52" t="n">
         <v>99.00182237673239</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B53" t="n">
-        <v>37.71324675733629</v>
+        <v>33.2659706126088</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2396,30 +2395,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F53" t="n">
-        <v>61.68664747332606</v>
+        <v>52.43023754066715</v>
       </c>
       <c r="G53" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H53" t="n">
-        <v>47.19931396082868</v>
+        <v>19.78233926113934</v>
       </c>
       <c r="I53" t="n">
         <v>145.1079291781629</v>
       </c>
       <c r="J53" t="n">
-        <v>47.75243896640717</v>
+        <v>26.08522277384196</v>
       </c>
       <c r="K53" t="n">
         <v>145.1079291781629</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B54" t="n">
-        <v>100.1741158725217</v>
+        <v>101.4234953930463</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2433,30 +2432,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F54" t="n">
-        <v>123.5675582301309</v>
+        <v>125.1624220808657</v>
       </c>
       <c r="G54" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H54" t="n">
-        <v>108.8087900852936</v>
+        <v>91.8198779299797</v>
       </c>
       <c r="I54" t="n">
         <v>170.6021266410801</v>
       </c>
       <c r="J54" t="n">
-        <v>109.539194669198</v>
+        <v>100.3277221996216</v>
       </c>
       <c r="K54" t="n">
         <v>170.6021266410801</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B55" t="n">
-        <v>133.1501245805496</v>
+        <v>133.7409817141819</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2470,30 +2469,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F55" t="n">
-        <v>131.9929336509338</v>
+        <v>132.1600648161539</v>
       </c>
       <c r="G55" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H55" t="n">
-        <v>129.613083138453</v>
+        <v>132.1600648161539</v>
       </c>
       <c r="I55" t="n">
         <v>186.3654577987215</v>
       </c>
       <c r="J55" t="n">
-        <v>129.8468180600035</v>
+        <v>130.7436374366726</v>
       </c>
       <c r="K55" t="n">
         <v>186.3654577987215</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B56" t="n">
-        <v>129.8452417348777</v>
+        <v>128.5372472740891</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2507,26 +2506,26 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F56" t="n">
-        <v>128.6417360972979</v>
+        <v>126.0334396152739</v>
       </c>
       <c r="G56" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H56" t="n">
-        <v>127.496160402067</v>
+        <v>126.0271187226832</v>
       </c>
       <c r="I56" t="n">
         <v>196.9121654022667</v>
       </c>
       <c r="J56" t="n">
-        <v>128.641736097298</v>
+        <v>125.8168577127797</v>
       </c>
       <c r="K56" t="n">
         <v>196.9121654022667</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B57" t="n">
@@ -2563,7 +2562,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B58" t="n">
@@ -2600,7 +2599,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B59" t="n">
@@ -2637,7 +2636,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B60" t="n">
@@ -2674,7 +2673,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B61" t="n">
@@ -2711,11 +2710,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
-        <v>5.390960831321691</v>
+        <v>0</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2729,30 +2728,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F62" t="n">
-        <v>7.431975120799262</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H62" t="n">
-        <v>9.985517845505145</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="J62" t="n">
-        <v>8.708746483152197</v>
+        <v>0.0765134582850311</v>
       </c>
       <c r="K62" t="n">
         <v>367.7844877318893</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B63" t="n">
-        <v>5.390960831321691</v>
+        <v>0</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2766,30 +2765,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F63" t="n">
-        <v>7.431975120799262</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H63" t="n">
-        <v>9.985517845505145</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="J63" t="n">
-        <v>8.708746483152197</v>
+        <v>0.0765134582850311</v>
       </c>
       <c r="K63" t="n">
         <v>367.7844877318893</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B64" t="n">
-        <v>30.84878977067423</v>
+        <v>11.81795235831538</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2803,30 +2802,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F64" t="n">
-        <v>30.83561229464117</v>
+        <v>12.43772910740415</v>
       </c>
       <c r="G64" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H64" t="n">
-        <v>43.80545006768904</v>
+        <v>12.01261213163469</v>
       </c>
       <c r="I64" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="J64" t="n">
-        <v>44.06609030356653</v>
+        <v>12.8254933807642</v>
       </c>
       <c r="K64" t="n">
         <v>367.7844877318893</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B65" t="n">
-        <v>34.73194113869577</v>
+        <v>19.96709880551396</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2840,30 +2839,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F65" t="n">
-        <v>35.88913206831159</v>
+        <v>21.54801570354187</v>
       </c>
       <c r="G65" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H65" t="n">
-        <v>52.37690542790054</v>
+        <v>21.5480157035419</v>
       </c>
       <c r="I65" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="J65" t="n">
-        <v>51.96395438051304</v>
+        <v>22.96444308302326</v>
       </c>
       <c r="K65" t="n">
         <v>367.7844877318893</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B66" t="n">
-        <v>38.03682398436765</v>
+        <v>25.1708332456067</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2877,26 +2876,26 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F66" t="n">
-        <v>39.24032962194748</v>
+        <v>27.67464090442187</v>
       </c>
       <c r="G66" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H66" t="n">
-        <v>54.49382816428654</v>
+        <v>27.6809617970126</v>
       </c>
       <c r="I66" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="J66" t="n">
-        <v>53.16903634321852</v>
+        <v>27.89122280691614</v>
       </c>
       <c r="K66" t="n">
         <v>367.7844877318893</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B67" t="n">
@@ -2933,7 +2932,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B68" t="n">
@@ -2970,7 +2969,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B69" t="n">
@@ -3007,7 +3006,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B70" t="n">
@@ -3044,7 +3043,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B71" t="n">
@@ -3081,7 +3080,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B72" t="n">
@@ -3108,17 +3107,17 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>13.51852984003681</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>13.51852984003681</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B73" t="n">
@@ -3145,17 +3144,17 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>22.56322263436963</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>22.56322263436963</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B74" t="n">
@@ -3182,17 +3181,17 @@
         <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>29.38661214352011</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>29.38661214352011</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B75" t="n">
@@ -3219,17 +3218,17 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>34.83064310153793</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>34.83064310153793</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B76" t="n">
@@ -3256,21 +3255,21 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>39.33805076686722</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>39.33805076686722</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B77" t="n">
-        <v>29.09155481394678</v>
+        <v>24.87272280247809</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -3284,30 +3283,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F77" t="n">
-        <v>2.309209281532209</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H77" t="n">
-        <v>18.04087623720322</v>
+        <v>34.48251564526847</v>
       </c>
       <c r="I77" t="n">
-        <v>13.51852984003681</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J77" t="n">
-        <v>18.04087623720322</v>
+        <v>25.4281462684566</v>
       </c>
       <c r="K77" t="n">
-        <v>13.51852984003681</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B78" t="n">
-        <v>29.09155481394678</v>
+        <v>24.87272280247809</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3321,30 +3320,30 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F78" t="n">
-        <v>2.309209281532209</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H78" t="n">
-        <v>18.04087623720322</v>
+        <v>34.48251564526847</v>
       </c>
       <c r="I78" t="n">
-        <v>22.56322263436963</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J78" t="n">
-        <v>18.04087623720322</v>
+        <v>25.42814626845661</v>
       </c>
       <c r="K78" t="n">
-        <v>22.56322263436963</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B79" t="n">
-        <v>29.09155481394678</v>
+        <v>24.87272280247809</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3358,26 +3357,26 @@
         <v>367.7844877318893</v>
       </c>
       <c r="F79" t="n">
-        <v>2.309209281532209</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
         <v>367.7844877318893</v>
       </c>
       <c r="H79" t="n">
-        <v>18.04087623720322</v>
+        <v>34.48251564526847</v>
       </c>
       <c r="I79" t="n">
-        <v>29.38661214352011</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J79" t="n">
-        <v>18.04087623720322</v>
+        <v>25.4281462684566</v>
       </c>
       <c r="K79" t="n">
-        <v>29.38661214352011</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B80" t="n">
@@ -3404,17 +3403,17 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>34.83064310153793</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>34.83064310153793</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B81" t="n">
@@ -3441,17 +3440,17 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>39.33805076686722</v>
+        <v>367.7844877318893</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>39.33805076686722</v>
+        <v>367.7844877318893</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B82" t="n">
@@ -3486,7 +3485,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B83" t="n">
@@ -3521,7 +3520,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B84" t="n">
@@ -3556,7 +3555,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B85" t="n">
@@ -3591,7 +3590,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B86" t="n">
@@ -3626,7 +3625,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B87" t="n">
@@ -3661,7 +3660,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B88" t="n">
@@ -3696,7 +3695,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B89" t="n">
@@ -3731,7 +3730,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B90" t="n">
@@ -3766,7 +3765,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B91" t="n">
@@ -3801,7 +3800,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B92" t="n">
@@ -3836,7 +3835,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B93" t="n">
@@ -3871,7 +3870,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B94" t="n">
@@ -3906,7 +3905,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B95" t="n">
@@ -3941,7 +3940,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B96" t="n">
